--- a/administrasi/Daftar Nilai Paket B.xlsx
+++ b/administrasi/Daftar Nilai Paket B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\semester-pkbm\administrasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A36F11-8B82-4B27-9338-067AAE25ED54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEC2FC8-2193-4BD4-BFAF-9C68C2A76F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rekap Bangun Rejo" sheetId="1" r:id="rId1"/>
@@ -505,6 +505,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -514,22 +517,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1027,58 +1027,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
     </row>
     <row r="4" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14" ht="24.95" customHeight="1"/>
@@ -1136,9 +1136,15 @@
       <c r="C7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="D7" s="13">
+        <v>35</v>
+      </c>
+      <c r="E7" s="13">
+        <v>85</v>
+      </c>
+      <c r="F7" s="13">
+        <v>75</v>
+      </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
@@ -1158,9 +1164,15 @@
       <c r="C8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="D8" s="13">
+        <v>33</v>
+      </c>
+      <c r="E8" s="13">
+        <v>45</v>
+      </c>
+      <c r="F8" s="13">
+        <v>55</v>
+      </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
@@ -1180,9 +1192,15 @@
       <c r="C9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="D9" s="13">
+        <v>53</v>
+      </c>
+      <c r="E9" s="13">
+        <v>47.5</v>
+      </c>
+      <c r="F9" s="13">
+        <v>70</v>
+      </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
@@ -1202,9 +1220,15 @@
       <c r="C10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="D10" s="13">
+        <v>40</v>
+      </c>
+      <c r="E10" s="13">
+        <v>47.5</v>
+      </c>
+      <c r="F10" s="13">
+        <v>65</v>
+      </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
@@ -1224,9 +1248,15 @@
       <c r="C11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="D11" s="13">
+        <v>40</v>
+      </c>
+      <c r="E11" s="13">
+        <v>45</v>
+      </c>
+      <c r="F11" s="13">
+        <v>67.5</v>
+      </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
@@ -1243,12 +1273,18 @@
       <c r="B12" s="11">
         <v>3116653493</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="D12" s="13">
+        <v>58</v>
+      </c>
+      <c r="E12" s="13">
+        <v>40</v>
+      </c>
+      <c r="F12" s="13">
+        <v>60</v>
+      </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
@@ -1268,9 +1304,15 @@
       <c r="C13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="D13" s="13">
+        <v>25</v>
+      </c>
+      <c r="E13" s="13">
+        <v>52.5</v>
+      </c>
+      <c r="F13" s="13">
+        <v>37.5</v>
+      </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
@@ -1290,9 +1332,15 @@
       <c r="C14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="D14" s="13">
+        <v>48</v>
+      </c>
+      <c r="E14" s="13">
+        <v>50</v>
+      </c>
+      <c r="F14" s="13">
+        <v>65</v>
+      </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
@@ -1312,9 +1360,15 @@
       <c r="C15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="D15" s="13">
+        <v>38</v>
+      </c>
+      <c r="E15" s="13">
+        <v>47.5</v>
+      </c>
+      <c r="F15" s="13">
+        <v>70</v>
+      </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
@@ -1334,9 +1388,15 @@
       <c r="C16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="D16" s="13">
+        <v>38</v>
+      </c>
+      <c r="E16" s="13">
+        <v>42.5</v>
+      </c>
+      <c r="F16" s="13">
+        <v>92.5</v>
+      </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
@@ -1356,9 +1416,15 @@
       <c r="C17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="D17" s="13">
+        <v>28</v>
+      </c>
+      <c r="E17" s="13">
+        <v>42.5</v>
+      </c>
+      <c r="F17" s="13">
+        <v>50</v>
+      </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
@@ -1378,9 +1444,15 @@
       <c r="C18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="D18" s="13">
+        <v>38</v>
+      </c>
+      <c r="E18" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="F18" s="13">
+        <v>50</v>
+      </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
@@ -1436,58 +1508,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
     </row>
     <row r="4" spans="1:14 16384:16384" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14 16384:16384" s="1" customFormat="1" ht="36" customHeight="1">
@@ -1544,9 +1616,15 @@
       <c r="C6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
+      <c r="D6" s="22">
+        <v>38</v>
+      </c>
+      <c r="E6" s="22">
+        <v>27.5</v>
+      </c>
+      <c r="F6" s="23">
+        <v>50</v>
+      </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
@@ -1566,9 +1644,15 @@
       <c r="C7" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="23"/>
+      <c r="D7" s="22">
+        <v>38</v>
+      </c>
+      <c r="E7" s="22">
+        <v>55</v>
+      </c>
+      <c r="F7" s="23">
+        <v>70</v>
+      </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
       <c r="I7" s="23"/>
@@ -1588,9 +1672,15 @@
       <c r="C8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23"/>
+      <c r="D8" s="22">
+        <v>50</v>
+      </c>
+      <c r="E8" s="22">
+        <v>65</v>
+      </c>
+      <c r="F8" s="23">
+        <v>77.5</v>
+      </c>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
       <c r="I8" s="23"/>
@@ -1610,9 +1700,15 @@
       <c r="C9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23"/>
+      <c r="D9" s="22">
+        <v>40</v>
+      </c>
+      <c r="E9" s="22">
+        <v>25</v>
+      </c>
+      <c r="F9" s="23">
+        <v>55</v>
+      </c>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
       <c r="I9" s="23"/>
@@ -1632,9 +1728,15 @@
       <c r="C10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="23"/>
+      <c r="D10" s="22">
+        <v>50</v>
+      </c>
+      <c r="E10" s="22">
+        <v>40</v>
+      </c>
+      <c r="F10" s="23">
+        <v>55</v>
+      </c>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
       <c r="I10" s="23"/>
@@ -1654,9 +1756,15 @@
       <c r="C11" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
+      <c r="D11" s="22">
+        <v>38</v>
+      </c>
+      <c r="E11" s="22">
+        <v>52.5</v>
+      </c>
+      <c r="F11" s="23">
+        <v>75</v>
+      </c>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
       <c r="I11" s="23"/>
@@ -1676,9 +1784,15 @@
       <c r="C12" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
+      <c r="D12" s="22">
+        <v>23</v>
+      </c>
+      <c r="E12" s="22">
+        <v>65</v>
+      </c>
+      <c r="F12" s="23">
+        <v>55</v>
+      </c>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
       <c r="I12" s="23"/>
@@ -1698,9 +1812,15 @@
       <c r="C13" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
+      <c r="D13" s="22">
+        <v>43</v>
+      </c>
+      <c r="E13" s="22">
+        <v>50</v>
+      </c>
+      <c r="F13" s="23">
+        <v>67.5</v>
+      </c>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
       <c r="I13" s="23"/>
@@ -1871,28 +1991,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
     </row>
     <row r="4" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
       <c r="A4" s="5"/>
@@ -1901,10 +2021,10 @@
       <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" ht="21" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="4" t="s">
         <v>55</v>
       </c>
@@ -2000,7 +2120,7 @@
       <c r="B14" s="11">
         <v>3116653493</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="31" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="13"/>
@@ -2174,16 +2294,16 @@
       <c r="D28" s="13"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="35"/>
+      <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="35"/>
+      <c r="D31" s="38"/>
     </row>
     <row r="32" spans="1:4">
       <c r="C32" s="3"/>
@@ -2195,10 +2315,10 @@
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="35"/>
+      <c r="D35" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/administrasi/Daftar Nilai Paket B.xlsx
+++ b/administrasi/Daftar Nilai Paket B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\semester-pkbm\administrasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEC2FC8-2193-4BD4-BFAF-9C68C2A76F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3FFB5A-4247-48A9-8FF1-4434F8B5AC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,16 +511,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1045,40 +1045,40 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
     </row>
     <row r="3" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
     </row>
     <row r="4" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14" ht="24.95" customHeight="1"/>
@@ -1145,9 +1145,15 @@
       <c r="F7" s="13">
         <v>75</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="G7" s="13">
+        <v>40</v>
+      </c>
+      <c r="H7" s="13">
+        <v>22</v>
+      </c>
+      <c r="I7" s="13">
+        <v>45</v>
+      </c>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
@@ -1173,9 +1179,15 @@
       <c r="F8" s="13">
         <v>55</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
+      <c r="G8" s="13">
+        <v>33</v>
+      </c>
+      <c r="H8" s="13">
+        <v>55</v>
+      </c>
+      <c r="I8" s="13">
+        <v>31</v>
+      </c>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
@@ -1201,9 +1213,15 @@
       <c r="F9" s="13">
         <v>70</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="G9" s="13">
+        <v>16</v>
+      </c>
+      <c r="H9" s="13">
+        <v>55</v>
+      </c>
+      <c r="I9" s="13">
+        <v>34</v>
+      </c>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
@@ -1229,9 +1247,15 @@
       <c r="F10" s="13">
         <v>65</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="G10" s="13">
+        <v>30</v>
+      </c>
+      <c r="H10" s="13">
+        <v>50</v>
+      </c>
+      <c r="I10" s="13">
+        <v>35</v>
+      </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
@@ -1257,9 +1281,15 @@
       <c r="F11" s="13">
         <v>67.5</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="G11" s="13">
+        <v>3</v>
+      </c>
+      <c r="H11" s="13">
+        <v>25</v>
+      </c>
+      <c r="I11" s="13">
+        <v>36</v>
+      </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
@@ -1285,9 +1315,15 @@
       <c r="F12" s="13">
         <v>60</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
+      <c r="G12" s="13">
+        <v>30</v>
+      </c>
+      <c r="H12" s="13">
+        <v>45</v>
+      </c>
+      <c r="I12" s="13">
+        <v>35</v>
+      </c>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
@@ -1313,9 +1349,15 @@
       <c r="F13" s="13">
         <v>37.5</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="G13" s="13">
+        <v>23</v>
+      </c>
+      <c r="H13" s="13">
+        <v>35</v>
+      </c>
+      <c r="I13" s="13">
+        <v>34</v>
+      </c>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
@@ -1341,9 +1383,15 @@
       <c r="F14" s="13">
         <v>65</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
+      <c r="G14" s="13">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13">
+        <v>45</v>
+      </c>
+      <c r="I14" s="13">
+        <v>48</v>
+      </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
@@ -1369,9 +1417,15 @@
       <c r="F15" s="13">
         <v>70</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="G15" s="13">
+        <v>16</v>
+      </c>
+      <c r="H15" s="13">
+        <v>30</v>
+      </c>
+      <c r="I15" s="13">
+        <v>35</v>
+      </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
@@ -1397,9 +1451,15 @@
       <c r="F16" s="13">
         <v>92.5</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="G16" s="13">
+        <v>36</v>
+      </c>
+      <c r="H16" s="13">
+        <v>55</v>
+      </c>
+      <c r="I16" s="13">
+        <v>35</v>
+      </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
@@ -1425,9 +1485,15 @@
       <c r="F17" s="13">
         <v>50</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="G17" s="13">
+        <v>30</v>
+      </c>
+      <c r="H17" s="13">
+        <v>25</v>
+      </c>
+      <c r="I17" s="13">
+        <v>36</v>
+      </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
@@ -1453,9 +1519,15 @@
       <c r="F18" s="13">
         <v>50</v>
       </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="G18" s="13">
+        <v>36</v>
+      </c>
+      <c r="H18" s="2">
+        <v>33</v>
+      </c>
+      <c r="I18" s="13">
+        <v>40</v>
+      </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
@@ -1511,8 +1583,8 @@
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
       <c r="F1" s="32"/>
@@ -1526,40 +1598,40 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
     </row>
     <row r="3" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="37"/>
       <c r="C3" s="37"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
     </row>
     <row r="4" spans="1:14 16384:16384" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14 16384:16384" s="1" customFormat="1" ht="36" customHeight="1">
@@ -1625,9 +1697,15 @@
       <c r="F6" s="23">
         <v>50</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
+      <c r="G6" s="22">
+        <v>23</v>
+      </c>
+      <c r="H6" s="22">
+        <v>53</v>
+      </c>
+      <c r="I6" s="23">
+        <v>36</v>
+      </c>
       <c r="J6" s="22"/>
       <c r="K6" s="22"/>
       <c r="L6" s="23"/>
@@ -1653,9 +1731,15 @@
       <c r="F7" s="23">
         <v>70</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="23"/>
+      <c r="G7" s="22">
+        <v>30</v>
+      </c>
+      <c r="H7" s="22">
+        <v>53</v>
+      </c>
+      <c r="I7" s="23">
+        <v>39</v>
+      </c>
       <c r="J7" s="22"/>
       <c r="K7" s="22"/>
       <c r="L7" s="23"/>
@@ -1681,9 +1765,15 @@
       <c r="F8" s="23">
         <v>77.5</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="23"/>
+      <c r="G8" s="22">
+        <v>26</v>
+      </c>
+      <c r="H8" s="22">
+        <v>43</v>
+      </c>
+      <c r="I8" s="23">
+        <v>42</v>
+      </c>
       <c r="J8" s="22"/>
       <c r="K8" s="22"/>
       <c r="L8" s="23"/>
@@ -1709,9 +1799,15 @@
       <c r="F9" s="23">
         <v>55</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="23"/>
+      <c r="G9" s="22">
+        <v>30</v>
+      </c>
+      <c r="H9" s="22">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <v>23</v>
+      </c>
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
       <c r="L9" s="23"/>
@@ -1737,9 +1833,15 @@
       <c r="F10" s="23">
         <v>55</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="23"/>
+      <c r="G10" s="22">
+        <v>40</v>
+      </c>
+      <c r="H10" s="22">
+        <v>43</v>
+      </c>
+      <c r="I10" s="23">
+        <v>39</v>
+      </c>
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
       <c r="L10" s="23"/>
@@ -1765,9 +1867,15 @@
       <c r="F11" s="23">
         <v>75</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="23"/>
+      <c r="G11" s="22">
+        <v>30</v>
+      </c>
+      <c r="H11" s="22">
+        <v>43</v>
+      </c>
+      <c r="I11" s="23">
+        <v>25</v>
+      </c>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="23"/>
@@ -1793,9 +1901,15 @@
       <c r="F12" s="23">
         <v>55</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="23"/>
+      <c r="G12" s="22">
+        <v>26</v>
+      </c>
+      <c r="H12" s="22">
+        <v>38</v>
+      </c>
+      <c r="I12" s="23">
+        <v>31</v>
+      </c>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
       <c r="L12" s="23"/>
@@ -1821,9 +1935,15 @@
       <c r="F13" s="23">
         <v>67.5</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="23"/>
+      <c r="G13" s="22">
+        <v>36</v>
+      </c>
+      <c r="H13" s="22">
+        <v>33</v>
+      </c>
+      <c r="I13" s="23">
+        <v>28</v>
+      </c>
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
       <c r="L13" s="23"/>
@@ -1999,20 +2119,20 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
     </row>
     <row r="4" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
       <c r="A4" s="5"/>

--- a/administrasi/Daftar Nilai Paket B.xlsx
+++ b/administrasi/Daftar Nilai Paket B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\semester-pkbm\administrasi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\Laporan PKBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3FFB5A-4247-48A9-8FF1-4434F8B5AC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF27855F-2552-498C-A78E-08703C51C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rekap Bangun Rejo" sheetId="1" r:id="rId1"/>
@@ -419,7 +419,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -482,10 +482,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -511,16 +507,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1027,62 +1023,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
     </row>
     <row r="3" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
     </row>
     <row r="4" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14" ht="24.95" customHeight="1"/>
-    <row r="6" spans="1:14" ht="38.1" customHeight="1">
+    <row r="6" spans="1:14" ht="38.1" customHeight="1" thickBot="1">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
@@ -1126,7 +1122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+    <row r="7" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A7" s="10">
         <v>1</v>
       </c>
@@ -1136,31 +1132,41 @@
       <c r="C7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>35</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <v>85</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="11">
         <v>75</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="11">
         <v>40</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="11">
         <v>22</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="11">
         <v>45</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J7" s="11">
+        <v>85</v>
+      </c>
+      <c r="K7" s="11">
+        <v>70</v>
+      </c>
+      <c r="L7" s="11">
+        <v>38</v>
+      </c>
+      <c r="M7" s="11">
+        <v>38</v>
+      </c>
+      <c r="N7" s="11">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A8" s="10">
         <v>2</v>
       </c>
@@ -1170,31 +1176,41 @@
       <c r="C8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>33</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <v>45</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="11">
         <v>55</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="11">
         <v>33</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="11">
         <v>55</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="11">
         <v>31</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-    </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J8" s="11">
+        <v>93</v>
+      </c>
+      <c r="K8" s="11">
+        <v>65</v>
+      </c>
+      <c r="L8" s="11">
+        <v>36</v>
+      </c>
+      <c r="M8" s="11">
+        <v>36</v>
+      </c>
+      <c r="N8" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A9" s="10">
         <v>3</v>
       </c>
@@ -1204,31 +1220,41 @@
       <c r="C9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>53</v>
       </c>
-      <c r="E9" s="13">
-        <v>47.5</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="E9" s="11">
+        <v>48</v>
+      </c>
+      <c r="F9" s="11">
         <v>70</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="11">
         <v>16</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="11">
         <v>55</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="11">
         <v>34</v>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-    </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J9" s="11">
+        <v>93</v>
+      </c>
+      <c r="K9" s="11">
+        <v>68</v>
+      </c>
+      <c r="L9" s="11">
+        <v>46</v>
+      </c>
+      <c r="M9" s="11">
+        <v>46</v>
+      </c>
+      <c r="N9" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A10" s="10">
         <v>4</v>
       </c>
@@ -1238,31 +1264,41 @@
       <c r="C10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <v>40</v>
       </c>
-      <c r="E10" s="13">
-        <v>47.5</v>
-      </c>
-      <c r="F10" s="13">
+      <c r="E10" s="11">
+        <v>48</v>
+      </c>
+      <c r="F10" s="11">
         <v>65</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="11">
         <v>30</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="11">
         <v>50</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="11">
         <v>35</v>
       </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-    </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J10" s="11">
+        <v>90</v>
+      </c>
+      <c r="K10" s="11">
+        <v>80</v>
+      </c>
+      <c r="L10" s="11">
+        <v>46</v>
+      </c>
+      <c r="M10" s="11">
+        <v>46</v>
+      </c>
+      <c r="N10" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A11" s="10">
         <v>5</v>
       </c>
@@ -1272,65 +1308,85 @@
       <c r="C11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="11">
         <v>40</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="11">
         <v>45</v>
       </c>
-      <c r="F11" s="13">
-        <v>67.5</v>
-      </c>
-      <c r="G11" s="13">
-        <v>3</v>
-      </c>
-      <c r="H11" s="13">
+      <c r="F11" s="11">
+        <v>68</v>
+      </c>
+      <c r="G11" s="11">
+        <v>33</v>
+      </c>
+      <c r="H11" s="11">
         <v>25</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="11">
         <v>36</v>
       </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-    </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J11" s="11">
+        <v>93</v>
+      </c>
+      <c r="K11" s="11">
+        <v>73</v>
+      </c>
+      <c r="L11" s="11">
+        <v>40</v>
+      </c>
+      <c r="M11" s="11">
+        <v>40</v>
+      </c>
+      <c r="N11" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A12" s="10">
         <v>6</v>
       </c>
       <c r="B12" s="11">
         <v>3116653493</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="11">
         <v>58</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="11">
         <v>40</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="11">
         <v>60</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="11">
         <v>30</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="11">
         <v>45</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="11">
         <v>35</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-    </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J12" s="11">
+        <v>88</v>
+      </c>
+      <c r="K12" s="11">
+        <v>55</v>
+      </c>
+      <c r="L12" s="11">
+        <v>30</v>
+      </c>
+      <c r="M12" s="11">
+        <v>30</v>
+      </c>
+      <c r="N12" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A13" s="10">
         <v>7</v>
       </c>
@@ -1340,31 +1396,41 @@
       <c r="C13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="11">
         <v>25</v>
       </c>
-      <c r="E13" s="13">
-        <v>52.5</v>
-      </c>
-      <c r="F13" s="13">
-        <v>37.5</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="E13" s="11">
+        <v>53</v>
+      </c>
+      <c r="F13" s="11">
+        <v>38</v>
+      </c>
+      <c r="G13" s="11">
         <v>23</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="11">
         <v>35</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="11">
         <v>34</v>
       </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J13" s="11">
+        <v>80</v>
+      </c>
+      <c r="K13" s="11">
+        <v>43</v>
+      </c>
+      <c r="L13" s="11">
+        <v>40</v>
+      </c>
+      <c r="M13" s="11">
+        <v>40</v>
+      </c>
+      <c r="N13" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A14" s="10">
         <v>8</v>
       </c>
@@ -1374,31 +1440,41 @@
       <c r="C14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="11">
         <v>48</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <v>50</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="11">
         <v>65</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="11">
         <v>20</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="11">
         <v>45</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>48</v>
       </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-    </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J14" s="11">
+        <v>88</v>
+      </c>
+      <c r="K14" s="11">
+        <v>73</v>
+      </c>
+      <c r="L14" s="11">
+        <v>38</v>
+      </c>
+      <c r="M14" s="11">
+        <v>38</v>
+      </c>
+      <c r="N14" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A15" s="10">
         <v>9</v>
       </c>
@@ -1408,31 +1484,41 @@
       <c r="C15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="11">
         <v>38</v>
       </c>
-      <c r="E15" s="13">
-        <v>47.5</v>
-      </c>
-      <c r="F15" s="13">
+      <c r="E15" s="11">
+        <v>48</v>
+      </c>
+      <c r="F15" s="11">
         <v>70</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="11">
         <v>16</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="11">
         <v>30</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="11">
         <v>35</v>
       </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-    </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J15" s="11">
+        <v>93</v>
+      </c>
+      <c r="K15" s="11">
+        <v>63</v>
+      </c>
+      <c r="L15" s="11">
+        <v>38</v>
+      </c>
+      <c r="M15" s="11">
+        <v>38</v>
+      </c>
+      <c r="N15" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A16" s="10">
         <v>10</v>
       </c>
@@ -1442,65 +1528,85 @@
       <c r="C16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="11">
         <v>38</v>
       </c>
-      <c r="E16" s="13">
-        <v>42.5</v>
-      </c>
-      <c r="F16" s="13">
-        <v>92.5</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="E16" s="11">
+        <v>43</v>
+      </c>
+      <c r="F16" s="11">
+        <v>93</v>
+      </c>
+      <c r="G16" s="11">
         <v>36</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="11">
         <v>55</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="11">
         <v>35</v>
       </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-    </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J16" s="11">
+        <v>90</v>
+      </c>
+      <c r="K16" s="11">
+        <v>43</v>
+      </c>
+      <c r="L16" s="11">
+        <v>48</v>
+      </c>
+      <c r="M16" s="11">
+        <v>48</v>
+      </c>
+      <c r="N16" s="11">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A17" s="10">
         <v>11</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="11">
         <v>28</v>
       </c>
-      <c r="E17" s="13">
-        <v>42.5</v>
-      </c>
-      <c r="F17" s="13">
+      <c r="E17" s="11">
+        <v>43</v>
+      </c>
+      <c r="F17" s="11">
         <v>50</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="11">
         <v>30</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="11">
         <v>25</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="11">
         <v>36</v>
       </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-    </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1">
+      <c r="J17" s="11">
+        <v>88</v>
+      </c>
+      <c r="K17" s="11">
+        <v>43</v>
+      </c>
+      <c r="L17" s="11">
+        <v>36</v>
+      </c>
+      <c r="M17" s="11">
+        <v>36</v>
+      </c>
+      <c r="N17" s="11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A18" s="10">
         <v>12</v>
       </c>
@@ -1510,46 +1616,56 @@
       <c r="C18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="11">
         <v>38</v>
       </c>
-      <c r="E18" s="13">
-        <v>32.5</v>
-      </c>
-      <c r="F18" s="13">
+      <c r="E18" s="11">
+        <v>33</v>
+      </c>
+      <c r="F18" s="11">
         <v>50</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="11">
         <v>36</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="11">
         <v>33</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="11">
         <v>40</v>
       </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
+      <c r="J18" s="11">
+        <v>88</v>
+      </c>
+      <c r="K18" s="11">
+        <v>43</v>
+      </c>
+      <c r="L18" s="11">
+        <v>36</v>
+      </c>
+      <c r="M18" s="11">
+        <v>36</v>
+      </c>
+      <c r="N18" s="11">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="20" spans="1:14" ht="15" customHeight="1">
-      <c r="C20" s="28"/>
-      <c r="I20" s="26" t="s">
+      <c r="C20" s="26"/>
+      <c r="I20" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="24.95" customHeight="1">
-      <c r="C21" s="28"/>
-      <c r="I21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:14" ht="15.75">
-      <c r="I22" s="26"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:14" ht="15.75">
-      <c r="I23" s="26" t="s">
+      <c r="I23" s="24" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1580,61 +1696,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
     </row>
     <row r="3" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
     </row>
     <row r="4" spans="1:14 16384:16384" ht="24.95" customHeight="1"/>
-    <row r="5" spans="1:14 16384:16384" s="1" customFormat="1" ht="36" customHeight="1">
+    <row r="5" spans="1:14 16384:16384" s="1" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1678,75 +1794,95 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+    <row r="6" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A6" s="21">
         <v>1</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="28" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="27">
         <v>38</v>
       </c>
-      <c r="E6" s="22">
-        <v>27.5</v>
-      </c>
-      <c r="F6" s="23">
+      <c r="E6" s="27">
+        <v>28</v>
+      </c>
+      <c r="F6" s="27">
         <v>50</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="27">
         <v>23</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="27">
         <v>53</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="27">
         <v>36</v>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-    </row>
-    <row r="7" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+      <c r="J6" s="27">
+        <v>93</v>
+      </c>
+      <c r="K6" s="27">
+        <v>65</v>
+      </c>
+      <c r="L6" s="27">
+        <v>46</v>
+      </c>
+      <c r="M6" s="27">
+        <v>46</v>
+      </c>
+      <c r="N6" s="27">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A7" s="10">
         <v>2</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="27">
         <v>38</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="27">
         <v>55</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="27">
         <v>70</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="27">
         <v>30</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="27">
         <v>53</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="27">
         <v>39</v>
       </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-    </row>
-    <row r="8" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+      <c r="J7" s="27">
+        <v>93</v>
+      </c>
+      <c r="K7" s="27">
+        <v>78</v>
+      </c>
+      <c r="L7" s="27">
+        <v>56</v>
+      </c>
+      <c r="M7" s="27">
+        <v>56</v>
+      </c>
+      <c r="N7" s="27">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -1756,336 +1892,396 @@
       <c r="C8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="27">
         <v>50</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="27">
         <v>65</v>
       </c>
-      <c r="F8" s="23">
-        <v>77.5</v>
-      </c>
-      <c r="G8" s="22">
+      <c r="F8" s="27">
+        <v>78</v>
+      </c>
+      <c r="G8" s="27">
         <v>26</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="27">
         <v>43</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="27">
         <v>42</v>
       </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-    </row>
-    <row r="9" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+      <c r="J8" s="27">
+        <v>83</v>
+      </c>
+      <c r="K8" s="27">
+        <v>68</v>
+      </c>
+      <c r="L8" s="27">
+        <v>42</v>
+      </c>
+      <c r="M8" s="27">
+        <v>42</v>
+      </c>
+      <c r="N8" s="27">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A9" s="10">
         <v>4</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="27" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="27">
         <v>40</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="27">
         <v>25</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="27">
         <v>55</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="27">
         <v>30</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="27">
         <v>30</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="27">
         <v>23</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-    </row>
-    <row r="10" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+      <c r="J9" s="27">
+        <v>93</v>
+      </c>
+      <c r="K9" s="27">
+        <v>55</v>
+      </c>
+      <c r="L9" s="27">
+        <v>32</v>
+      </c>
+      <c r="M9" s="27">
+        <v>32</v>
+      </c>
+      <c r="N9" s="27">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A10" s="10">
         <v>5</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="27" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="27">
         <v>50</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="27">
         <v>40</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="27">
         <v>55</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="27">
         <v>40</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="27">
         <v>43</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="27">
         <v>39</v>
       </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-    </row>
-    <row r="11" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+      <c r="J10" s="27">
+        <v>90</v>
+      </c>
+      <c r="K10" s="27">
+        <v>68</v>
+      </c>
+      <c r="L10" s="27">
+        <v>48</v>
+      </c>
+      <c r="M10" s="27">
+        <v>48</v>
+      </c>
+      <c r="N10" s="27">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A11" s="10">
         <v>6</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="27" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="27">
         <v>38</v>
       </c>
-      <c r="E11" s="22">
-        <v>52.5</v>
-      </c>
-      <c r="F11" s="23">
+      <c r="E11" s="27">
+        <v>53</v>
+      </c>
+      <c r="F11" s="27">
         <v>75</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="27">
         <v>30</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="27">
         <v>43</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="27">
         <v>25</v>
       </c>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-    </row>
-    <row r="12" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+      <c r="J11" s="27">
+        <v>90</v>
+      </c>
+      <c r="K11" s="27">
+        <v>60</v>
+      </c>
+      <c r="L11" s="27">
+        <v>52</v>
+      </c>
+      <c r="M11" s="27">
+        <v>52</v>
+      </c>
+      <c r="N11" s="27">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A12" s="10">
         <v>7</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="27" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="27">
         <v>23</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="27">
         <v>65</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="27">
         <v>55</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="27">
         <v>26</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="27">
         <v>38</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="27">
         <v>31</v>
       </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-    </row>
-    <row r="13" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1">
+      <c r="J12" s="27">
+        <v>93</v>
+      </c>
+      <c r="K12" s="27">
+        <v>75</v>
+      </c>
+      <c r="L12" s="27">
+        <v>34</v>
+      </c>
+      <c r="M12" s="27">
+        <v>34</v>
+      </c>
+      <c r="N12" s="27">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A13" s="10">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="27" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="27">
         <v>43</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="27">
         <v>50</v>
       </c>
-      <c r="F13" s="23">
-        <v>67.5</v>
-      </c>
-      <c r="G13" s="22">
+      <c r="F13" s="27">
+        <v>68</v>
+      </c>
+      <c r="G13" s="27">
         <v>36</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="27">
         <v>33</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="27">
         <v>28</v>
       </c>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
+      <c r="J13" s="27">
+        <v>85</v>
+      </c>
+      <c r="K13" s="27">
+        <v>70</v>
+      </c>
+      <c r="L13" s="27">
+        <v>56</v>
+      </c>
+      <c r="M13" s="27">
+        <v>56</v>
+      </c>
+      <c r="N13" s="27">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:14 16384:16384" s="1" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
       <c r="XFD14"/>
     </row>
     <row r="15" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
     </row>
     <row r="16" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
     </row>
     <row r="17" spans="1:14 16384:16384" s="1" customFormat="1">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
       <c r="XFD17"/>
     </row>
     <row r="18" spans="1:14 16384:16384" s="1" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26" t="s">
+      <c r="A18" s="22"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
       <c r="XFD18"/>
     </row>
     <row r="19" spans="1:14 16384:16384" s="1" customFormat="1">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
       <c r="XFD19"/>
     </row>
     <row r="20" spans="1:14 16384:16384" s="1" customFormat="1">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
       <c r="XFD20"/>
     </row>
     <row r="21" spans="1:14 16384:16384" s="1" customFormat="1">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
       <c r="XFD21"/>
     </row>
   </sheetData>
@@ -2111,28 +2307,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
       <c r="A4" s="5"/>
@@ -2141,10 +2337,10 @@
       <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" ht="21" customHeight="1">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="39"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="4" t="s">
         <v>55</v>
       </c>
@@ -2240,7 +2436,7 @@
       <c r="B14" s="11">
         <v>3116653493</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="13"/>
@@ -2297,7 +2493,7 @@
       <c r="A19" s="10">
         <v>11</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -2321,7 +2517,7 @@
       <c r="A21" s="10">
         <v>13</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="28" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="14" t="s">
@@ -2333,7 +2529,7 @@
       <c r="A22" s="10">
         <v>14</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="15" t="s">
@@ -2357,7 +2553,7 @@
       <c r="A24" s="10">
         <v>16</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="27" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="15" t="s">
@@ -2369,7 +2565,7 @@
       <c r="A25" s="10">
         <v>17</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="27" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="15" t="s">
@@ -2381,7 +2577,7 @@
       <c r="A26" s="10">
         <v>18</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="27" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="15" t="s">
@@ -2393,7 +2589,7 @@
       <c r="A27" s="10">
         <v>19</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="27" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="15" t="s">
@@ -2405,7 +2601,7 @@
       <c r="A28" s="10">
         <v>20</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="27" t="s">
         <v>46</v>
       </c>
       <c r="C28" s="15" t="s">
@@ -2414,16 +2610,16 @@
       <c r="D28" s="13"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="38"/>
+      <c r="D30" s="36"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="38"/>
+      <c r="D31" s="36"/>
     </row>
     <row r="32" spans="1:4">
       <c r="C32" s="3"/>
@@ -2435,10 +2631,10 @@
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="38"/>
+      <c r="D35" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="7">
